--- a/public/base.xlsx
+++ b/public/base.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7590"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="176">
   <si>
     <t>کارگزاری آینده نگر خوارزمی به مدیریت دکتر ذوقی 09123011311 و 61914000-021 (داخلی 408 الی 411)</t>
   </si>
@@ -46,24 +46,15 @@
     <t>بنزن</t>
   </si>
   <si>
-    <t>پارا زایلین</t>
-  </si>
-  <si>
     <t>پروپان مایع</t>
   </si>
   <si>
-    <t>EPVC 7544 M</t>
-  </si>
-  <si>
     <t>پلی پروپیلن نساجی Z30S</t>
   </si>
   <si>
     <t>پلی پروپیلن نساجی HP565S</t>
   </si>
   <si>
-    <t>پلی پروپیلن شیمیایی_ZR340R</t>
-  </si>
-  <si>
     <t>پلی پروپیلن شیمیایی ZR230C</t>
   </si>
   <si>
@@ -79,12 +70,6 @@
     <t>پلی پروپیلن شیمیایی ZB332C</t>
   </si>
   <si>
-    <t>پلی پروپیلن شیمیایی RP 345S</t>
-  </si>
-  <si>
-    <t>پلی پروپیلن شیمیایی RP 230C</t>
-  </si>
-  <si>
     <t>پلی پروپیلن شیمیایی RG3212E</t>
   </si>
   <si>
@@ -121,9 +106,6 @@
     <t>پلی استایرن معمولی 1551</t>
   </si>
   <si>
-    <t>پلی استایرن انبساطی105-F</t>
-  </si>
-  <si>
     <t>پلی استایرن انبساطی نسوز  400-F</t>
   </si>
   <si>
@@ -154,9 +136,6 @@
     <t>پلی اتیلن سنگین دورانی 3840UA</t>
   </si>
   <si>
-    <t>پلی اتیلن سنگین تزریقی52B18UV</t>
-  </si>
-  <si>
     <t>پلی اتیلن سنگین تزریقی I‏4</t>
   </si>
   <si>
@@ -178,21 +157,12 @@
     <t>پلی اتیلن سنگین اکستروژن 7700M</t>
   </si>
   <si>
-    <t>پلی اتیلن سنگین اکستروژن 4460 HEX</t>
-  </si>
-  <si>
     <t>1و3 بوتادین</t>
   </si>
   <si>
     <t>اتیل بنزن</t>
   </si>
   <si>
-    <t>ارتوزایلین</t>
-  </si>
-  <si>
-    <t>استایرن منومر*</t>
-  </si>
-  <si>
     <t>اسید استیک</t>
   </si>
   <si>
@@ -202,18 +172,12 @@
     <t>اسید نیتریک</t>
   </si>
   <si>
-    <t>اوره پریل</t>
-  </si>
-  <si>
     <t>اوره پریل بدون فرمالدئید</t>
   </si>
   <si>
     <t>اوره پریل فله</t>
   </si>
   <si>
-    <t>اوره گرانوله</t>
-  </si>
-  <si>
     <t>اوره گرانوله فله</t>
   </si>
   <si>
@@ -223,21 +187,12 @@
     <t>آروماتیک سنگین</t>
   </si>
   <si>
-    <t>آلکیل بنزن خطی (LAB)</t>
-  </si>
-  <si>
     <t>آمونیاک (گاز)</t>
   </si>
   <si>
     <t>برش سنگین</t>
   </si>
   <si>
-    <t>بوتان</t>
-  </si>
-  <si>
-    <t>پروپان</t>
-  </si>
-  <si>
     <t>ردیف</t>
   </si>
   <si>
@@ -272,9 +227,6 @@
   </si>
   <si>
     <t>پلی اتیلن سنگین فیلم EX5</t>
-  </si>
-  <si>
-    <t>پلی استایرن انبساطی‏ R200</t>
   </si>
   <si>
     <t>پلی اتیلن سنگین فیلم ‏MFI3713</t>
@@ -304,9 +256,6 @@
     <t xml:space="preserve">مقایسه قیمت پایه پلی وینیل کلراید PVC(E) </t>
   </si>
   <si>
-    <t>EPVC 7244 H</t>
-  </si>
-  <si>
     <t>پلی وینیل کلراید E 7242</t>
   </si>
   <si>
@@ -400,18 +349,12 @@
     <t>متیلن دی فنیل دی ایزوسیانات KLM100-C</t>
   </si>
   <si>
-    <t>متیلن دی فنیل دی ایزوسیانات MDI پلیمری</t>
-  </si>
-  <si>
     <t>متیلن دی فنیل دی ایزوسیانات MDI پلیمری (KP600‏)</t>
   </si>
   <si>
     <t>متیلن دی فنیل دی ایزوسیانات MDI خالص</t>
   </si>
   <si>
-    <t>متیلن دی فنیل دی ایزوسیانات MDI خالص (KM70)</t>
-  </si>
-  <si>
     <t>متیلن دی فنیل دی ایزوسیانات 20-KCS</t>
   </si>
   <si>
@@ -424,9 +367,6 @@
     <t>تولوئن</t>
   </si>
   <si>
-    <t>دو اتیل هگزانول</t>
-  </si>
-  <si>
     <t>دی اتانول آمین</t>
   </si>
   <si>
@@ -451,13 +391,7 @@
     <t>منو اتیلن گلایکول</t>
   </si>
   <si>
-    <t>منومر وینیل استات</t>
-  </si>
-  <si>
     <t>نرمال بوتانول</t>
-  </si>
-  <si>
-    <t>نفت کوره _CFO</t>
   </si>
   <si>
     <t xml:space="preserve">مقایسه قیمت پایه محصولات شیمیایی  </t>
@@ -567,69 +501,6 @@
     <t>*</t>
   </si>
   <si>
-    <t>مقایسه قیمت پایه محصولات  پلی وینیل کلراید PVC(S)  مورخ تاریخ 1 و تاریخ 2 
-لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
-لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
-  </si>
-  <si>
-    <t>مقایسه قیمت پایه محصولات  پلی وینیل کلراید PVC(E)  مورخ تاریخ 1 و تاریخ 2 
-لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
-لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
-  </si>
-  <si>
-    <t>مقایسه قیمت پایه محصولات پلی پروپیلن نساجی مورخ تاریخ 1 و تاریخ 2 
-لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
-لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
-  </si>
-  <si>
-    <t>مقایسه قیمت پایه محصولات پلی پروپیلن شیمیایی مورخ تاریخ 1 و تاریخ 2 
-لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
-لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
-  </si>
-  <si>
-    <t>مقایسه قیمت پایه محصولات پلی اتیلن سنگین مورخ تاریخ 1 و تاریخ 2 
-لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
-لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
-  </si>
-  <si>
-    <t>مقایسه قیمت پایه محصولات پلی اتیلن سبک مورخ تاریخ 1 و تاریخ 2 
-لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
-لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
-  </si>
-  <si>
-    <t>مقایسه قیمت پایه محصولات پلی اتیلن ترفتالات بطری PET مورخ تاریخ 1 و تاریخ 2 
-لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
-لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
-  </si>
-  <si>
     <t>مقایسه قیمت پایه محصولات MDI &amp; TDI مورخ تاریخ 1 و تاریخ 2 
 لینک واتساپ⬇️       
 https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
@@ -639,40 +510,171 @@
 ble.ir/join/HLzkvyNxQu</t>
   </si>
   <si>
+    <t>مقایسه قیمت پایه محصولات  پلی وینیل کلراید PVC(S)  مورخ تاریخ 1 و تاریخ 2 
+لینک واتساپ⬇️
+https://chat.whatsapp.com/H3OyG1UwQyu9SMYZSXjwTg   
+لینک تلگرام⬅️
+https://t.me/PVC_S
+لینک بله⬅️
+ ble.ir/join/7XbosDoRGo</t>
+  </si>
+  <si>
+    <t>مقایسه قیمت پایه محصولات  پلی وینیل کلراید PVC(E)  مورخ تاریخ 1 و تاریخ 2 
+لینک واتساپ⬇️       
+https://chat.whatsapp.com/LhFNgEt7egF2ovPvtnRF0M
+لینک تلگرام⬅️
+https://t.me/PVC_E
+لینک بله⬅️ 
+ble.ir/join/7XbosDoRGo</t>
+  </si>
+  <si>
+    <t>مقایسه قیمت پایه محصولات پلی پروپیلن نساجی مورخ تاریخ 1 و تاریخ 2 
+لینک واتساپ⬇️       
+https://chat.whatsapp.com/FvKUqp5OhfA6eBxxviRrxo   
+لینک تلگرام⬇️
+https://t.me/ppnasaji
+لینک بله⬇️
+ble.ir/join/9EtgjLCnFv</t>
+  </si>
+  <si>
+    <t>مقایسه قیمت پایه محصولات پلی پروپیلن شیمیایی مورخ تاریخ 1 و تاریخ 2 
+لینک واتساپ⬇️       
+https://chat.whatsapp.com/JxWS75fiKxcA9VXa70xjSs    
+لینک تلگرام⬇️
+https://t.me/ppshimiaie
+لینک بله⬇️
+ble.ir/join/3gvEcFuSpr</t>
+  </si>
+  <si>
+    <t>مقایسه قیمت پایه محصولات پلی استایرن مورخ تاریخ 1 و تاریخ 2 
+لینک واتساپ⬇️       
+https://chat.whatsapp.com/EwLit37nbqfEXKIx3yNuEA
+تلگرام⬇️
+https://t.me/PS_Borse_Kala
+بله⬇️
+ble.ir/join/3XgRvLQM2w</t>
+  </si>
+  <si>
+    <t>مقایسه قیمت پایه محصولات پلی اتیلن سنگین مورخ تاریخ 1 و تاریخ 2 
+لینک واتساپ⬇️       
+  https://chat.whatsapp.com/JZHr5y0cVmWDnoNo0kRO4e   
+   لینک تلگرام⬅️
+https://t.me/HDPE_borskala
+لینک بله⬅️
+ble.ir/join/9g9DZDeMz6</t>
+  </si>
+  <si>
+    <t>مقایسه قیمت پایه محصولات پلی اتیلن سبک مورخ تاریخ 1 و تاریخ 2 
+لینک واتساپ⬇️       
+https://chat.whatsapp.com/LM6jQnS14xuL7UosSEOOdd
+لینک تلگرام⬇️
+https://t.me/LDPE_borskala
+لینک بله⬇️
+ble.ir/join/2q2yEVgReR</t>
+  </si>
+  <si>
+    <t>مقایسه قیمت پایه محصولات پلی اتیلن ترفتالات بطری PET مورخ تاریخ 1 و تاریخ 2 
+لینک واتساپ⬇️       
+https://chat.whatsapp.com/LM0hjBQLpDYBYoBz1FuaO2
+لینک تلگرام⬇️
+https://t.me/pet_preform
+لینک بله⬇️
+ble.ir/join/ARPoaUBPm6</t>
+  </si>
+  <si>
     <t>مقایسه قیمت پایه محصولات شیمیایی مورخ تاریخ 1 و تاریخ 2 
 لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
-لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
+https://chat.whatsapp.com/DSqXEC3WHOx9Tt7hcmTSHa
+تلگرام⬇️
+https://t.me/Chemical_Products
+بله⬇️
+ble.ir/join/22Q9jHPj9z</t>
   </si>
   <si>
     <t>مقایسه قیمت پایه محصولات DEG و MEG وTEG مورخ تاریخ 1 و تاریخ 2 
 لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
+https://chat.whatsapp.com/J94UkAEExjpEz03Oj9eAs7     
+لینک تلگرام⬅️https://t.me/MEG_DEG
 لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
+ble.ir/join/EY65U7sh4J</t>
   </si>
   <si>
     <t>مقایسه قیمت پایه محصولات پلیمری مورخ تاریخ 1 و تاریخ 2 
 لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
-لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
-  </si>
-  <si>
-    <t>مقایسه قیمت پایه محصولات پلی استایرن مورخ تاریخ 1 و تاریخ 2 
-لینک واتساپ⬇️       
-https://chat.whatsapp.com/HBddSsmCnWAGot0Nvdauxs       
-لینک تلگرام⬇️       
-https://t.me/TDI_MDI
-لینک بله⬅️
-ble.ir/join/HLzkvyNxQu</t>
+ https://chat.whatsapp.com/BTXNtXtQBLrDOqxKlUq4NM
+تلگرام⬇️
+ https://t.me/Polymer_Products
+بله⬇️
+ble.ir/join/5Fiz2zcYQC</t>
+  </si>
+  <si>
+    <t>پلی وینیل کلراید E7244 H</t>
+  </si>
+  <si>
+    <t>پلی وینیل کلراید E7544 M</t>
+  </si>
+  <si>
+    <t>پلی پروپیلن شیمیاییRP230C</t>
+  </si>
+  <si>
+    <t>پلی پروپیلن شیمیاییRP345S</t>
+  </si>
+  <si>
+    <t>پلی پروپیلن شیمیایی ZR 340R</t>
+  </si>
+  <si>
+    <t>پلی استایرن انبساطی 200-R</t>
+  </si>
+  <si>
+    <t>پلی استایرن انبساطی 105-F</t>
+  </si>
+  <si>
+    <t>پلی اتیلن سنگین اکستروژن (HEX4460 )PE‏80</t>
+  </si>
+  <si>
+    <t>پلی اتیلن سنگین تزریقی 52B18UV</t>
+  </si>
+  <si>
+    <t>متیلن دی فنیل دی ایزوسیانات KM‏70 خالص</t>
+  </si>
+  <si>
+    <t>آلکیل بنزن خطی</t>
+  </si>
+  <si>
+    <t>ارتوزایلن</t>
+  </si>
+  <si>
+    <t>استایرن منومر</t>
+  </si>
+  <si>
+    <t>گاز بوتان</t>
+  </si>
+  <si>
+    <t>پارازایلین</t>
+  </si>
+  <si>
+    <t>گاز پروپان</t>
+  </si>
+  <si>
+    <t>دو اتیل هگزانول*</t>
+  </si>
+  <si>
+    <t>متیلن دی فنیل دی ایزوسیانات MDI پلیمری(KP‏200)</t>
+  </si>
+  <si>
+    <t>متیلن دی فنیل دی ایزوسیانات MDI پلیمری (KP‏600)</t>
+  </si>
+  <si>
+    <t>اوره پریل**</t>
+  </si>
+  <si>
+    <t>اوره گرانوله**</t>
+  </si>
+  <si>
+    <t>منومر وینیل استات *</t>
+  </si>
+  <si>
+    <t>نفت کوره</t>
   </si>
 </sst>
 </file>
@@ -1198,6 +1200,11 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="21" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1273,11 +1280,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1432,14 +1434,14 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1908046</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>936496</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>323849</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>179090</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>674390</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>1323974</xdr:rowOff>
     </xdr:to>
@@ -1458,7 +1460,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11233844035" y="676274"/>
+          <a:off x="11226557410" y="676274"/>
           <a:ext cx="5443369" cy="3657600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1470,16 +1472,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1555619</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1155569</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1464965</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>1228724</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>207665</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>323849</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1496,7 +1498,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11234196460" y="4600574"/>
+          <a:off x="11226338335" y="5276849"/>
           <a:ext cx="5443371" cy="3657600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1508,16 +1510,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1057499</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>238124</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>895574</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>417215</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>398145</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>160040</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>169545</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1534,8 +1536,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11233605910" y="12506324"/>
-          <a:ext cx="6532041" cy="4389120"/>
+          <a:off x="11228443360" y="18640424"/>
+          <a:ext cx="6532041" cy="4389121"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1698,16 +1700,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1812796</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1431796</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>83840</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>102890</xdr:colOff>
       <xdr:row>148</xdr:row>
-      <xdr:rowOff>698047</xdr:rowOff>
+      <xdr:rowOff>964747</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1724,8 +1726,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11233939285" y="44548425"/>
-          <a:ext cx="5443369" cy="3657600"/>
+          <a:off x="11230557910" y="60845700"/>
+          <a:ext cx="5443369" cy="3660322"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1736,16 +1738,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1360974</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>56049</xdr:colOff>
       <xdr:row>160</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>312440</xdr:colOff>
-      <xdr:row>171</xdr:row>
-      <xdr:rowOff>304799</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>93365</xdr:colOff>
+      <xdr:row>172</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1762,7 +1764,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11233710685" y="51444524"/>
+          <a:off x="11231253235" y="69542024"/>
           <a:ext cx="6123791" cy="4114800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1774,16 +1776,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1103801</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>522776</xdr:colOff>
       <xdr:row>188</xdr:row>
-      <xdr:rowOff>95249</xdr:rowOff>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>55265</xdr:colOff>
-      <xdr:row>199</xdr:row>
-      <xdr:rowOff>333375</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>64790</xdr:colOff>
+      <xdr:row>200</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1800,8 +1802,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11233967860" y="60855224"/>
-          <a:ext cx="6123789" cy="4114800"/>
+          <a:off x="11229224410" y="80705324"/>
+          <a:ext cx="6123789" cy="4114801"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1850,16 +1852,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1162050</xdr:colOff>
-      <xdr:row>226</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1038225</xdr:colOff>
+      <xdr:row>225</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>116736</xdr:colOff>
-      <xdr:row>238</xdr:row>
-      <xdr:rowOff>358</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>392961</xdr:colOff>
+      <xdr:row>237</xdr:row>
+      <xdr:rowOff>38458</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1876,8 +1878,59 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11233906389" y="73161525"/>
-          <a:ext cx="6127011" cy="4115157"/>
+          <a:off x="11230267839" y="96326325"/>
+          <a:ext cx="6127011" cy="4115158"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1323975</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E656D71-A6CD-C2A9-E037-6BEDD49CFAAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:alphaModFix amt="10000"/>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11233861200" y="1400174"/>
+          <a:ext cx="6219825" cy="1724025"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2170,7 +2223,7 @@
         <v>9</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
@@ -2184,24 +2237,24 @@
       </c>
     </row>
     <row r="2" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
+      <c r="A2" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
     </row>
     <row r="3" spans="1:34" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="82"/>
+      <c r="A3" s="82" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="83"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="85"/>
     </row>
     <row r="4" spans="1:34" s="57" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="62"/>
@@ -2251,7 +2304,7 @@
     </row>
     <row r="5" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B5" s="60" t="s">
         <v>3</v>
@@ -2270,7 +2323,7 @@
     <row r="6" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14"/>
       <c r="B6" s="43" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -2286,7 +2339,7 @@
     <row r="7" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14"/>
       <c r="B7" s="43" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -2302,7 +2355,7 @@
     <row r="8" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14"/>
       <c r="B8" s="44" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -2318,7 +2371,7 @@
     <row r="9" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14"/>
       <c r="B9" s="44" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -2333,7 +2386,7 @@
     </row>
     <row r="10" spans="1:34" s="24" customFormat="1" ht="24.75" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="38" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B10" s="45"/>
       <c r="C10" s="21"/>
@@ -2342,14 +2395,14 @@
       <c r="F10" s="23"/>
     </row>
     <row r="11" spans="1:34" ht="145.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="66" t="s">
-        <v>163</v>
-      </c>
-      <c r="B11" s="74"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="75"/>
+      <c r="A11" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="78"/>
     </row>
     <row r="12" spans="1:34" s="24" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="38"/>
@@ -2360,24 +2413,24 @@
       <c r="F12" s="23"/>
     </row>
     <row r="13" spans="1:34" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
+      <c r="A13" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
     </row>
     <row r="14" spans="1:34" s="57" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="80"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="82"/>
+      <c r="A14" s="82" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="83"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="85"/>
       <c r="G14" s="56"/>
       <c r="H14" s="56"/>
       <c r="I14" s="56"/>
@@ -2455,7 +2508,7 @@
     </row>
     <row r="16" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B16" s="60" t="s">
         <v>3</v>
@@ -2474,7 +2527,7 @@
     <row r="17" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14"/>
       <c r="B17" s="46" t="s">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
@@ -2490,7 +2543,7 @@
     <row r="18" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14"/>
       <c r="B18" s="46" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -2506,7 +2559,7 @@
     <row r="19" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14"/>
       <c r="B19" s="46" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
@@ -2522,7 +2575,7 @@
     <row r="20" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14"/>
       <c r="B20" s="46" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -2538,7 +2591,7 @@
     <row r="21" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="47" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
@@ -2554,7 +2607,7 @@
     <row r="22" spans="1:34" s="24" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14"/>
       <c r="B22" s="46" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
@@ -2569,7 +2622,7 @@
     </row>
     <row r="23" spans="1:34" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B23" s="48"/>
       <c r="C23" s="21"/>
@@ -2578,14 +2631,14 @@
       <c r="F23" s="23"/>
     </row>
     <row r="24" spans="1:34" s="26" customFormat="1" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="66" t="s">
-        <v>164</v>
-      </c>
-      <c r="B24" s="74"/>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="75"/>
+      <c r="A24" s="69" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="78"/>
       <c r="G24" s="25"/>
       <c r="H24" s="25"/>
       <c r="I24" s="25"/>
@@ -2624,27 +2677,27 @@
       <c r="F25" s="23"/>
     </row>
     <row r="26" spans="1:34" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="78"/>
-      <c r="C26" s="78"/>
-      <c r="D26" s="78"/>
-      <c r="E26" s="78"/>
-      <c r="F26" s="78"/>
+      <c r="A26" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
     </row>
     <row r="27" spans="1:34" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="79" t="s">
-        <v>160</v>
-      </c>
-      <c r="B27" s="80"/>
-      <c r="C27" s="81"/>
-      <c r="D27" s="81"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="82"/>
-    </row>
-    <row r="28" spans="1:34" s="92" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="90"/>
+      <c r="A27" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" s="83"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="85"/>
+    </row>
+    <row r="28" spans="1:34" s="67" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="65"/>
       <c r="B28" s="61" t="s">
         <v>5</v>
       </c>
@@ -2660,38 +2713,38 @@
       <c r="F28" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="G28" s="91"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="91"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="91"/>
-      <c r="M28" s="91"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="91"/>
-      <c r="P28" s="91"/>
-      <c r="Q28" s="91"/>
-      <c r="R28" s="91"/>
-      <c r="S28" s="91"/>
-      <c r="T28" s="91"/>
-      <c r="U28" s="91"/>
-      <c r="V28" s="91"/>
-      <c r="W28" s="91"/>
-      <c r="X28" s="91"/>
-      <c r="Y28" s="91"/>
-      <c r="Z28" s="91"/>
-      <c r="AA28" s="91"/>
-      <c r="AB28" s="91"/>
-      <c r="AC28" s="91"/>
-      <c r="AD28" s="91"/>
-      <c r="AE28" s="91"/>
-      <c r="AF28" s="91"/>
-      <c r="AG28" s="91"/>
-      <c r="AH28" s="91"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
+      <c r="L28" s="66"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="66"/>
+      <c r="P28" s="66"/>
+      <c r="Q28" s="66"/>
+      <c r="R28" s="66"/>
+      <c r="S28" s="66"/>
+      <c r="T28" s="66"/>
+      <c r="U28" s="66"/>
+      <c r="V28" s="66"/>
+      <c r="W28" s="66"/>
+      <c r="X28" s="66"/>
+      <c r="Y28" s="66"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
+      <c r="AB28" s="66"/>
+      <c r="AC28" s="66"/>
+      <c r="AD28" s="66"/>
+      <c r="AE28" s="66"/>
+      <c r="AF28" s="66"/>
+      <c r="AG28" s="66"/>
+      <c r="AH28" s="66"/>
     </row>
     <row r="29" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B29" s="60" t="s">
         <v>3</v>
@@ -2710,7 +2763,7 @@
     <row r="30" spans="1:34" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14"/>
       <c r="B30" s="49" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -2726,7 +2779,7 @@
     <row r="31" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17"/>
       <c r="B31" s="50" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -2741,7 +2794,7 @@
     </row>
     <row r="32" spans="1:34" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="39" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B32" s="51"/>
       <c r="C32" s="27"/>
@@ -2750,14 +2803,14 @@
       <c r="F32" s="29"/>
     </row>
     <row r="33" spans="1:34" ht="153.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="65" t="s">
-        <v>165</v>
-      </c>
-      <c r="B33" s="76"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
+      <c r="A33" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="79"/>
     </row>
     <row r="34" spans="1:34" s="63" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="38"/>
@@ -2796,27 +2849,27 @@
       <c r="AH34" s="24"/>
     </row>
     <row r="35" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-      <c r="F35" s="78"/>
+      <c r="A35" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
     </row>
     <row r="36" spans="1:34" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="B36" s="80"/>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="82"/>
-    </row>
-    <row r="37" spans="1:34" s="92" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="90"/>
+      <c r="A36" s="82" t="s">
+        <v>139</v>
+      </c>
+      <c r="B36" s="83"/>
+      <c r="C36" s="84"/>
+      <c r="D36" s="84"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="85"/>
+    </row>
+    <row r="37" spans="1:34" s="67" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="65"/>
       <c r="B37" s="61" t="s">
         <v>5</v>
       </c>
@@ -2832,38 +2885,38 @@
       <c r="F37" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="G37" s="91"/>
-      <c r="H37" s="91"/>
-      <c r="I37" s="91"/>
-      <c r="J37" s="91"/>
-      <c r="K37" s="91"/>
-      <c r="L37" s="91"/>
-      <c r="M37" s="91"/>
-      <c r="N37" s="91"/>
-      <c r="O37" s="91"/>
-      <c r="P37" s="91"/>
-      <c r="Q37" s="91"/>
-      <c r="R37" s="91"/>
-      <c r="S37" s="91"/>
-      <c r="T37" s="91"/>
-      <c r="U37" s="91"/>
-      <c r="V37" s="91"/>
-      <c r="W37" s="91"/>
-      <c r="X37" s="91"/>
-      <c r="Y37" s="91"/>
-      <c r="Z37" s="91"/>
-      <c r="AA37" s="91"/>
-      <c r="AB37" s="91"/>
-      <c r="AC37" s="91"/>
-      <c r="AD37" s="91"/>
-      <c r="AE37" s="91"/>
-      <c r="AF37" s="91"/>
-      <c r="AG37" s="91"/>
-      <c r="AH37" s="91"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="66"/>
+      <c r="J37" s="66"/>
+      <c r="K37" s="66"/>
+      <c r="L37" s="66"/>
+      <c r="M37" s="66"/>
+      <c r="N37" s="66"/>
+      <c r="O37" s="66"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="66"/>
+      <c r="R37" s="66"/>
+      <c r="S37" s="66"/>
+      <c r="T37" s="66"/>
+      <c r="U37" s="66"/>
+      <c r="V37" s="66"/>
+      <c r="W37" s="66"/>
+      <c r="X37" s="66"/>
+      <c r="Y37" s="66"/>
+      <c r="Z37" s="66"/>
+      <c r="AA37" s="66"/>
+      <c r="AB37" s="66"/>
+      <c r="AC37" s="66"/>
+      <c r="AD37" s="66"/>
+      <c r="AE37" s="66"/>
+      <c r="AF37" s="66"/>
+      <c r="AG37" s="66"/>
+      <c r="AH37" s="66"/>
     </row>
     <row r="38" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B38" s="60" t="s">
         <v>3</v>
@@ -2882,7 +2935,7 @@
     <row r="39" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="32"/>
       <c r="B39" s="46" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="C39" s="33"/>
       <c r="D39" s="33"/>
@@ -2898,7 +2951,7 @@
     <row r="40" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="32"/>
       <c r="B40" s="46" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C40" s="33"/>
       <c r="D40" s="33"/>
@@ -2914,7 +2967,7 @@
     <row r="41" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="32"/>
       <c r="B41" s="46" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C41" s="33"/>
       <c r="D41" s="33"/>
@@ -2930,7 +2983,7 @@
     <row r="42" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="32"/>
       <c r="B42" s="46" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C42" s="33"/>
       <c r="D42" s="33"/>
@@ -2946,7 +2999,7 @@
     <row r="43" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="32"/>
       <c r="B43" s="46" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C43" s="33"/>
       <c r="D43" s="33"/>
@@ -2962,7 +3015,7 @@
     <row r="44" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="32"/>
       <c r="B44" s="46" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C44" s="33"/>
       <c r="D44" s="33"/>
@@ -2978,7 +3031,7 @@
     <row r="45" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="32"/>
       <c r="B45" s="46" t="s">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="C45" s="33"/>
       <c r="D45" s="33"/>
@@ -2994,7 +3047,7 @@
     <row r="46" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="32"/>
       <c r="B46" s="46" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="C46" s="33"/>
       <c r="D46" s="33"/>
@@ -3010,7 +3063,7 @@
     <row r="47" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="32"/>
       <c r="B47" s="46" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C47" s="33"/>
       <c r="D47" s="33"/>
@@ -3026,7 +3079,7 @@
     <row r="48" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="32"/>
       <c r="B48" s="46" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C48" s="33"/>
       <c r="D48" s="33"/>
@@ -3042,7 +3095,7 @@
     <row r="49" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="32"/>
       <c r="B49" s="46" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C49" s="33"/>
       <c r="D49" s="33"/>
@@ -3058,7 +3111,7 @@
     <row r="50" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="32"/>
       <c r="B50" s="46" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C50" s="33"/>
       <c r="D50" s="33"/>
@@ -3074,7 +3127,7 @@
     <row r="51" spans="1:6" s="24" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="32"/>
       <c r="B51" s="46" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C51" s="33"/>
       <c r="D51" s="33"/>
@@ -3090,7 +3143,7 @@
     <row r="52" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="32"/>
       <c r="B52" s="46" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C52" s="33"/>
       <c r="D52" s="33"/>
@@ -3106,7 +3159,7 @@
     <row r="53" spans="1:6" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="32"/>
       <c r="B53" s="46" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C53" s="33"/>
       <c r="D53" s="33"/>
@@ -3121,7 +3174,7 @@
     </row>
     <row r="54" spans="1:6" s="1" customFormat="1" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="38" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B54" s="52"/>
       <c r="C54" s="21"/>
@@ -3130,14 +3183,14 @@
       <c r="F54" s="31"/>
     </row>
     <row r="55" spans="1:6" s="1" customFormat="1" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="B55" s="67"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="68"/>
+      <c r="A55" s="69" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" s="70"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="71"/>
     </row>
     <row r="56" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="38"/>
@@ -3148,27 +3201,27 @@
       <c r="F56" s="31"/>
     </row>
     <row r="57" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B57" s="78"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
+      <c r="A57" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="81"/>
+      <c r="C57" s="81"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
     </row>
     <row r="58" spans="1:6" s="1" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="70" t="s">
-        <v>93</v>
-      </c>
-      <c r="B58" s="83"/>
-      <c r="C58" s="73"/>
-      <c r="D58" s="73"/>
-      <c r="E58" s="73"/>
-      <c r="F58" s="73"/>
+      <c r="A58" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="B58" s="86"/>
+      <c r="C58" s="76"/>
+      <c r="D58" s="76"/>
+      <c r="E58" s="76"/>
+      <c r="F58" s="76"/>
     </row>
     <row r="59" spans="1:6" s="56" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="90"/>
+      <c r="A59" s="65"/>
       <c r="B59" s="61" t="s">
         <v>5</v>
       </c>
@@ -3187,7 +3240,7 @@
     </row>
     <row r="60" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B60" s="60" t="s">
         <v>3</v>
@@ -3206,7 +3259,7 @@
     <row r="61" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="32"/>
       <c r="B61" s="46" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C61" s="33"/>
       <c r="D61" s="33"/>
@@ -3222,7 +3275,7 @@
     <row r="62" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="32"/>
       <c r="B62" s="46" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C62" s="33"/>
       <c r="D62" s="33"/>
@@ -3238,7 +3291,7 @@
     <row r="63" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="32"/>
       <c r="B63" s="46" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C63" s="33"/>
       <c r="D63" s="33"/>
@@ -3254,7 +3307,7 @@
     <row r="64" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="32"/>
       <c r="B64" s="46" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C64" s="33"/>
       <c r="D64" s="33"/>
@@ -3270,7 +3323,7 @@
     <row r="65" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="32"/>
       <c r="B65" s="46" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C65" s="33"/>
       <c r="D65" s="33"/>
@@ -3286,7 +3339,7 @@
     <row r="66" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="32"/>
       <c r="B66" s="46" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C66" s="33"/>
       <c r="D66" s="33"/>
@@ -3302,7 +3355,7 @@
     <row r="67" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="32"/>
       <c r="B67" s="46" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C67" s="33"/>
       <c r="D67" s="33"/>
@@ -3318,7 +3371,7 @@
     <row r="68" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="32"/>
       <c r="B68" s="46" t="s">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="C68" s="33"/>
       <c r="D68" s="33"/>
@@ -3334,7 +3387,7 @@
     <row r="69" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="32"/>
       <c r="B69" s="46" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C69" s="33"/>
       <c r="D69" s="33"/>
@@ -3350,7 +3403,7 @@
     <row r="70" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="32"/>
       <c r="B70" s="46" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C70" s="33"/>
       <c r="D70" s="33"/>
@@ -3366,7 +3419,7 @@
     <row r="71" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="32"/>
       <c r="B71" s="46" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C71" s="33"/>
       <c r="D71" s="33"/>
@@ -3382,7 +3435,7 @@
     <row r="72" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="32"/>
       <c r="B72" s="46" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C72" s="33"/>
       <c r="D72" s="33"/>
@@ -3398,7 +3451,7 @@
     <row r="73" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="32"/>
       <c r="B73" s="46" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C73" s="33"/>
       <c r="D73" s="33"/>
@@ -3414,7 +3467,7 @@
     <row r="74" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="32"/>
       <c r="B74" s="46" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C74" s="33"/>
       <c r="D74" s="33"/>
@@ -3430,7 +3483,7 @@
     <row r="75" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="32"/>
       <c r="B75" s="46" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C75" s="33"/>
       <c r="D75" s="33"/>
@@ -3446,7 +3499,7 @@
     <row r="76" spans="1:6" s="24" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="32"/>
       <c r="B76" s="46" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C76" s="33"/>
       <c r="D76" s="33"/>
@@ -3462,7 +3515,7 @@
     <row r="77" spans="1:6" s="2" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="32"/>
       <c r="B77" s="46" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C77" s="33"/>
       <c r="D77" s="33"/>
@@ -3478,7 +3531,7 @@
     <row r="78" spans="1:6" s="2" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="32"/>
       <c r="B78" s="46" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="C78" s="33"/>
       <c r="D78" s="33"/>
@@ -3493,7 +3546,7 @@
     </row>
     <row r="79" spans="1:6" s="1" customFormat="1" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B79" s="53"/>
       <c r="C79" s="21"/>
@@ -3502,14 +3555,14 @@
       <c r="F79" s="31"/>
     </row>
     <row r="80" spans="1:6" s="1" customFormat="1" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="66" t="s">
-        <v>174</v>
-      </c>
-      <c r="B80" s="67"/>
-      <c r="C80" s="67"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="67"/>
-      <c r="F80" s="68"/>
+      <c r="A80" s="69" t="s">
+        <v>146</v>
+      </c>
+      <c r="B80" s="70"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="70"/>
+      <c r="F80" s="71"/>
     </row>
     <row r="81" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="38"/>
@@ -3520,27 +3573,27 @@
       <c r="F81" s="31"/>
     </row>
     <row r="82" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="84" t="s">
-        <v>0</v>
-      </c>
-      <c r="B82" s="85"/>
-      <c r="C82" s="85"/>
-      <c r="D82" s="85"/>
-      <c r="E82" s="85"/>
-      <c r="F82" s="86"/>
+      <c r="A82" s="87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="88"/>
+      <c r="C82" s="88"/>
+      <c r="D82" s="88"/>
+      <c r="E82" s="88"/>
+      <c r="F82" s="89"/>
     </row>
     <row r="83" spans="1:6" s="1" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="70" t="s">
-        <v>94</v>
-      </c>
-      <c r="B83" s="71"/>
-      <c r="C83" s="72"/>
-      <c r="D83" s="72"/>
-      <c r="E83" s="72"/>
-      <c r="F83" s="72"/>
+      <c r="A83" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B83" s="74"/>
+      <c r="C83" s="75"/>
+      <c r="D83" s="75"/>
+      <c r="E83" s="75"/>
+      <c r="F83" s="75"/>
     </row>
     <row r="84" spans="1:6" s="56" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="90"/>
+      <c r="A84" s="65"/>
       <c r="B84" s="61" t="s">
         <v>5</v>
       </c>
@@ -3559,7 +3612,7 @@
     </row>
     <row r="85" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B85" s="60" t="s">
         <v>3</v>
@@ -3578,7 +3631,7 @@
     <row r="86" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="17"/>
       <c r="B86" s="46" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
@@ -3594,7 +3647,7 @@
     <row r="87" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17"/>
       <c r="B87" s="46" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -3610,7 +3663,7 @@
     <row r="88" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="17"/>
       <c r="B88" s="46" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -3626,7 +3679,7 @@
     <row r="89" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17"/>
       <c r="B89" s="46" t="s">
-        <v>44</v>
+        <v>161</v>
       </c>
       <c r="C89" s="14"/>
       <c r="D89" s="14"/>
@@ -3642,7 +3695,7 @@
     <row r="90" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="17"/>
       <c r="B90" s="46" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C90" s="14"/>
       <c r="D90" s="14"/>
@@ -3658,7 +3711,7 @@
     <row r="91" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17"/>
       <c r="B91" s="46" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C91" s="14"/>
       <c r="D91" s="14"/>
@@ -3674,7 +3727,7 @@
     <row r="92" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="17"/>
       <c r="B92" s="46" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
@@ -3690,7 +3743,7 @@
     <row r="93" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17"/>
       <c r="B93" s="46" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="14"/>
@@ -3706,7 +3759,7 @@
     <row r="94" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="17"/>
       <c r="B94" s="46" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C94" s="14"/>
       <c r="D94" s="14"/>
@@ -3722,7 +3775,7 @@
     <row r="95" spans="1:6" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17"/>
       <c r="B95" s="46" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C95" s="14"/>
       <c r="D95" s="14"/>
@@ -3738,7 +3791,7 @@
     <row r="96" spans="1:6" s="24" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="17"/>
       <c r="B96" s="46" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C96" s="14"/>
       <c r="D96" s="14"/>
@@ -3754,7 +3807,7 @@
     <row r="97" spans="1:34" s="3" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17"/>
       <c r="B97" s="46" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
@@ -3798,7 +3851,7 @@
     <row r="98" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="17"/>
       <c r="B98" s="46" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C98" s="14"/>
       <c r="D98" s="14"/>
@@ -3814,7 +3867,7 @@
     <row r="99" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17"/>
       <c r="B99" s="46" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="C99" s="14"/>
       <c r="D99" s="14"/>
@@ -3829,7 +3882,7 @@
     </row>
     <row r="100" spans="1:34" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="38" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B100" s="53"/>
       <c r="C100" s="21"/>
@@ -3838,14 +3891,14 @@
       <c r="F100" s="31"/>
     </row>
     <row r="101" spans="1:34" ht="161.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="66" t="s">
-        <v>167</v>
-      </c>
-      <c r="B101" s="67"/>
-      <c r="C101" s="67"/>
-      <c r="D101" s="67"/>
-      <c r="E101" s="67"/>
-      <c r="F101" s="68"/>
+      <c r="A101" s="69" t="s">
+        <v>147</v>
+      </c>
+      <c r="B101" s="70"/>
+      <c r="C101" s="70"/>
+      <c r="D101" s="70"/>
+      <c r="E101" s="70"/>
+      <c r="F101" s="71"/>
     </row>
     <row r="102" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="38"/>
@@ -3856,27 +3909,27 @@
       <c r="F102" s="31"/>
     </row>
     <row r="103" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B103" s="73"/>
-      <c r="C103" s="73"/>
-      <c r="D103" s="73"/>
-      <c r="E103" s="73"/>
-      <c r="F103" s="73"/>
+      <c r="A103" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B103" s="76"/>
+      <c r="C103" s="76"/>
+      <c r="D103" s="76"/>
+      <c r="E103" s="76"/>
+      <c r="F103" s="76"/>
     </row>
     <row r="104" spans="1:34" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="70" t="s">
-        <v>107</v>
-      </c>
-      <c r="B104" s="71"/>
-      <c r="C104" s="72"/>
-      <c r="D104" s="72"/>
-      <c r="E104" s="72"/>
-      <c r="F104" s="72"/>
+      <c r="A104" s="73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B104" s="74"/>
+      <c r="C104" s="75"/>
+      <c r="D104" s="75"/>
+      <c r="E104" s="75"/>
+      <c r="F104" s="75"/>
     </row>
     <row r="105" spans="1:34" s="57" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="90"/>
+      <c r="A105" s="65"/>
       <c r="B105" s="61" t="s">
         <v>5</v>
       </c>
@@ -3923,7 +3976,7 @@
     </row>
     <row r="106" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B106" s="60" t="s">
         <v>3</v>
@@ -3942,7 +3995,7 @@
     <row r="107" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17"/>
       <c r="B107" s="46" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C107" s="14"/>
       <c r="D107" s="14"/>
@@ -3958,7 +4011,7 @@
     <row r="108" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="34"/>
       <c r="B108" s="46" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C108" s="14"/>
       <c r="D108" s="14"/>
@@ -3974,7 +4027,7 @@
     <row r="109" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="34"/>
       <c r="B109" s="46" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
@@ -3990,7 +4043,7 @@
     <row r="110" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="34"/>
       <c r="B110" s="46" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C110" s="14"/>
       <c r="D110" s="14"/>
@@ -4006,7 +4059,7 @@
     <row r="111" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="34"/>
       <c r="B111" s="46" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C111" s="14"/>
       <c r="D111" s="14"/>
@@ -4022,7 +4075,7 @@
     <row r="112" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="34"/>
       <c r="B112" s="46" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
@@ -4038,7 +4091,7 @@
     <row r="113" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="34"/>
       <c r="B113" s="46" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
@@ -4054,7 +4107,7 @@
     <row r="114" spans="1:34" s="24" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="34"/>
       <c r="B114" s="46" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C114" s="14"/>
       <c r="D114" s="14"/>
@@ -4070,7 +4123,7 @@
     <row r="115" spans="1:34" s="3" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="34"/>
       <c r="B115" s="46" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C115" s="14"/>
       <c r="D115" s="14"/>
@@ -4114,7 +4167,7 @@
     <row r="116" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="34"/>
       <c r="B116" s="46" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
@@ -4130,7 +4183,7 @@
     <row r="117" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="34"/>
       <c r="B117" s="46" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
@@ -4146,7 +4199,7 @@
     <row r="118" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="34"/>
       <c r="B118" s="46" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C118" s="14"/>
       <c r="D118" s="14"/>
@@ -4161,7 +4214,7 @@
     </row>
     <row r="119" spans="1:34" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="36" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B119" s="54"/>
       <c r="C119" s="24"/>
@@ -4170,14 +4223,14 @@
       <c r="F119" s="24"/>
     </row>
     <row r="120" spans="1:34" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="66" t="s">
-        <v>168</v>
-      </c>
-      <c r="B120" s="67"/>
-      <c r="C120" s="67"/>
-      <c r="D120" s="67"/>
-      <c r="E120" s="67"/>
-      <c r="F120" s="68"/>
+      <c r="A120" s="69" t="s">
+        <v>148</v>
+      </c>
+      <c r="B120" s="70"/>
+      <c r="C120" s="70"/>
+      <c r="D120" s="70"/>
+      <c r="E120" s="70"/>
+      <c r="F120" s="71"/>
     </row>
     <row r="121" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="36"/>
@@ -4188,27 +4241,27 @@
       <c r="F121" s="24"/>
     </row>
     <row r="122" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B122" s="73"/>
-      <c r="C122" s="73"/>
-      <c r="D122" s="73"/>
-      <c r="E122" s="73"/>
-      <c r="F122" s="73"/>
+      <c r="A122" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B122" s="76"/>
+      <c r="C122" s="76"/>
+      <c r="D122" s="76"/>
+      <c r="E122" s="76"/>
+      <c r="F122" s="76"/>
     </row>
     <row r="123" spans="1:34" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="70" t="s">
-        <v>116</v>
-      </c>
-      <c r="B123" s="71"/>
-      <c r="C123" s="72"/>
-      <c r="D123" s="72"/>
-      <c r="E123" s="72"/>
-      <c r="F123" s="72"/>
+      <c r="A123" s="73" t="s">
+        <v>99</v>
+      </c>
+      <c r="B123" s="74"/>
+      <c r="C123" s="75"/>
+      <c r="D123" s="75"/>
+      <c r="E123" s="75"/>
+      <c r="F123" s="75"/>
     </row>
     <row r="124" spans="1:34" s="57" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="90"/>
+      <c r="A124" s="65"/>
       <c r="B124" s="61" t="s">
         <v>5</v>
       </c>
@@ -4255,7 +4308,7 @@
     </row>
     <row r="125" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B125" s="60" t="s">
         <v>3</v>
@@ -4274,7 +4327,7 @@
     <row r="126" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="17"/>
       <c r="B126" s="46" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C126" s="14"/>
       <c r="D126" s="14"/>
@@ -4290,7 +4343,7 @@
     <row r="127" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="34"/>
       <c r="B127" s="46" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C127" s="14"/>
       <c r="D127" s="14"/>
@@ -4306,7 +4359,7 @@
     <row r="128" spans="1:34" s="37" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="34"/>
       <c r="B128" s="46" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C128" s="14"/>
       <c r="D128" s="14"/>
@@ -4322,7 +4375,7 @@
     <row r="129" spans="1:34" s="3" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="34"/>
       <c r="B129" s="46" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C129" s="14"/>
       <c r="D129" s="14"/>
@@ -4366,7 +4419,7 @@
     <row r="130" spans="1:34" s="3" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="34"/>
       <c r="B130" s="46" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C130" s="14"/>
       <c r="D130" s="14"/>
@@ -4410,7 +4463,7 @@
     <row r="131" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="34"/>
       <c r="B131" s="46" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="C131" s="14"/>
       <c r="D131" s="14"/>
@@ -4426,7 +4479,7 @@
     <row r="132" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="34"/>
       <c r="B132" s="46" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C132" s="14"/>
       <c r="D132" s="14"/>
@@ -4442,7 +4495,7 @@
     <row r="133" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="34"/>
       <c r="B133" s="46" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="C133" s="14"/>
       <c r="D133" s="14"/>
@@ -4457,7 +4510,7 @@
     </row>
     <row r="134" spans="1:34" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="36" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B134" s="55"/>
       <c r="C134" s="37"/>
@@ -4466,14 +4519,14 @@
       <c r="F134" s="37"/>
     </row>
     <row r="135" spans="1:34" ht="147" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="66" t="s">
-        <v>169</v>
-      </c>
-      <c r="B135" s="67"/>
-      <c r="C135" s="67"/>
-      <c r="D135" s="67"/>
-      <c r="E135" s="67"/>
-      <c r="F135" s="68"/>
+      <c r="A135" s="69" t="s">
+        <v>149</v>
+      </c>
+      <c r="B135" s="70"/>
+      <c r="C135" s="70"/>
+      <c r="D135" s="70"/>
+      <c r="E135" s="70"/>
+      <c r="F135" s="71"/>
     </row>
     <row r="136" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="36"/>
@@ -4484,27 +4537,27 @@
       <c r="F136" s="37"/>
     </row>
     <row r="137" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B137" s="73"/>
-      <c r="C137" s="73"/>
-      <c r="D137" s="73"/>
-      <c r="E137" s="73"/>
-      <c r="F137" s="73"/>
+      <c r="A137" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B137" s="76"/>
+      <c r="C137" s="76"/>
+      <c r="D137" s="76"/>
+      <c r="E137" s="76"/>
+      <c r="F137" s="76"/>
     </row>
     <row r="138" spans="1:34" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="70" t="s">
-        <v>117</v>
-      </c>
-      <c r="B138" s="71"/>
-      <c r="C138" s="72"/>
-      <c r="D138" s="72"/>
-      <c r="E138" s="72"/>
-      <c r="F138" s="72"/>
+      <c r="A138" s="73" t="s">
+        <v>100</v>
+      </c>
+      <c r="B138" s="74"/>
+      <c r="C138" s="75"/>
+      <c r="D138" s="75"/>
+      <c r="E138" s="75"/>
+      <c r="F138" s="75"/>
     </row>
     <row r="139" spans="1:34" s="57" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="90"/>
+      <c r="A139" s="65"/>
       <c r="B139" s="61" t="s">
         <v>5</v>
       </c>
@@ -4551,7 +4604,7 @@
     </row>
     <row r="140" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B140" s="60" t="s">
         <v>3</v>
@@ -4570,7 +4623,7 @@
     <row r="141" spans="1:34" s="24" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17"/>
       <c r="B141" s="46" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C141" s="14"/>
       <c r="D141" s="14"/>
@@ -4586,7 +4639,7 @@
     <row r="142" spans="1:34" s="3" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="34"/>
       <c r="B142" s="46" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C142" s="14"/>
       <c r="D142" s="14"/>
@@ -4630,7 +4683,7 @@
     <row r="143" spans="1:34" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="34"/>
       <c r="B143" s="46" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="C143" s="14"/>
       <c r="D143" s="14"/>
@@ -4646,7 +4699,7 @@
     <row r="144" spans="1:34" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="34"/>
       <c r="B144" s="46" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C144" s="14"/>
       <c r="D144" s="14"/>
@@ -4662,7 +4715,7 @@
     <row r="145" spans="1:34" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="34"/>
       <c r="B145" s="46" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="C145" s="14"/>
       <c r="D145" s="14"/>
@@ -4678,7 +4731,7 @@
     <row r="146" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="34"/>
       <c r="B146" s="46" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="C146" s="14"/>
       <c r="D146" s="14"/>
@@ -4694,7 +4747,7 @@
     <row r="147" spans="1:34" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="34"/>
       <c r="B147" s="46" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="C147" s="14"/>
       <c r="D147" s="14"/>
@@ -4709,7 +4762,7 @@
     </row>
     <row r="148" spans="1:34" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="36" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B148" s="54"/>
       <c r="C148" s="24"/>
@@ -4718,14 +4771,14 @@
       <c r="F148" s="24"/>
     </row>
     <row r="149" spans="1:34" ht="143.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="66" t="s">
-        <v>170</v>
-      </c>
-      <c r="B149" s="67"/>
-      <c r="C149" s="67"/>
-      <c r="D149" s="67"/>
-      <c r="E149" s="67"/>
-      <c r="F149" s="68"/>
+      <c r="A149" s="69" t="s">
+        <v>141</v>
+      </c>
+      <c r="B149" s="70"/>
+      <c r="C149" s="70"/>
+      <c r="D149" s="70"/>
+      <c r="E149" s="70"/>
+      <c r="F149" s="71"/>
     </row>
     <row r="150" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="36"/>
@@ -4736,27 +4789,27 @@
       <c r="F150" s="24"/>
     </row>
     <row r="151" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B151" s="73"/>
-      <c r="C151" s="73"/>
-      <c r="D151" s="73"/>
-      <c r="E151" s="73"/>
-      <c r="F151" s="73"/>
+      <c r="A151" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B151" s="76"/>
+      <c r="C151" s="76"/>
+      <c r="D151" s="76"/>
+      <c r="E151" s="76"/>
+      <c r="F151" s="76"/>
     </row>
     <row r="152" spans="1:34" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="71" t="s">
-        <v>86</v>
-      </c>
-      <c r="B152" s="71"/>
-      <c r="C152" s="72"/>
-      <c r="D152" s="72"/>
-      <c r="E152" s="72"/>
-      <c r="F152" s="72"/>
+      <c r="A152" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="B152" s="74"/>
+      <c r="C152" s="75"/>
+      <c r="D152" s="75"/>
+      <c r="E152" s="75"/>
+      <c r="F152" s="75"/>
     </row>
     <row r="153" spans="1:34" s="57" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="90"/>
+      <c r="A153" s="65"/>
       <c r="B153" s="61" t="s">
         <v>5</v>
       </c>
@@ -4803,7 +4856,7 @@
     </row>
     <row r="154" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B154" s="60" t="s">
         <v>3</v>
@@ -4822,7 +4875,7 @@
     <row r="155" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="14"/>
       <c r="B155" s="46" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C155" s="14"/>
       <c r="D155" s="14"/>
@@ -4838,7 +4891,7 @@
     <row r="156" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="34"/>
       <c r="B156" s="46" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C156" s="14"/>
       <c r="D156" s="14"/>
@@ -4854,7 +4907,7 @@
     <row r="157" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="34"/>
       <c r="B157" s="46" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="C157" s="14"/>
       <c r="D157" s="14"/>
@@ -4870,7 +4923,7 @@
     <row r="158" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="34"/>
       <c r="B158" s="46" t="s">
-        <v>56</v>
+        <v>165</v>
       </c>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
@@ -4886,7 +4939,7 @@
     <row r="159" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="34"/>
       <c r="B159" s="46" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C159" s="14"/>
       <c r="D159" s="14"/>
@@ -4902,7 +4955,7 @@
     <row r="160" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="34"/>
       <c r="B160" s="46" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C160" s="14"/>
       <c r="D160" s="14"/>
@@ -4918,7 +4971,7 @@
     <row r="161" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="34"/>
       <c r="B161" s="46" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C161" s="14"/>
       <c r="D161" s="14"/>
@@ -4934,7 +4987,7 @@
     <row r="162" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="34"/>
       <c r="B162" s="46" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="C162" s="14"/>
       <c r="D162" s="14"/>
@@ -4950,7 +5003,7 @@
     <row r="163" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="34"/>
       <c r="B163" s="46" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C163" s="14"/>
       <c r="D163" s="14"/>
@@ -4966,7 +5019,7 @@
     <row r="164" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="34"/>
       <c r="B164" s="46" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C164" s="14"/>
       <c r="D164" s="14"/>
@@ -4982,7 +5035,7 @@
     <row r="165" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="34"/>
       <c r="B165" s="46" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="C165" s="14"/>
       <c r="D165" s="14"/>
@@ -4998,7 +5051,7 @@
     <row r="166" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="34"/>
       <c r="B166" s="46" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C166" s="14"/>
       <c r="D166" s="14"/>
@@ -5014,7 +5067,7 @@
     <row r="167" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="34"/>
       <c r="B167" s="46" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C167" s="14"/>
       <c r="D167" s="14"/>
@@ -5030,7 +5083,7 @@
     <row r="168" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="34"/>
       <c r="B168" s="46" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C168" s="14"/>
       <c r="D168" s="14"/>
@@ -5046,7 +5099,7 @@
     <row r="169" spans="1:6" s="24" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="34"/>
       <c r="B169" s="46" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
       <c r="C169" s="14"/>
       <c r="D169" s="14"/>
@@ -5062,7 +5115,7 @@
     <row r="170" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="34"/>
       <c r="B170" s="46" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C170" s="14"/>
       <c r="D170" s="14"/>
@@ -5078,7 +5131,7 @@
     <row r="171" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="34"/>
       <c r="B171" s="46" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C171" s="14"/>
       <c r="D171" s="14"/>
@@ -5110,7 +5163,7 @@
     <row r="173" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="34"/>
       <c r="B173" s="46" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C173" s="14"/>
       <c r="D173" s="14"/>
@@ -5126,7 +5179,7 @@
     <row r="174" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="34"/>
       <c r="B174" s="46" t="s">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="C174" s="14"/>
       <c r="D174" s="14"/>
@@ -5142,7 +5195,7 @@
     <row r="175" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="34"/>
       <c r="B175" s="46" t="s">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="C175" s="14"/>
       <c r="D175" s="14"/>
@@ -5158,7 +5211,7 @@
     <row r="176" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="34"/>
       <c r="B176" s="46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C176" s="14"/>
       <c r="D176" s="14"/>
@@ -5173,7 +5226,7 @@
     </row>
     <row r="177" spans="1:34" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="36" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B177" s="53"/>
       <c r="C177" s="21"/>
@@ -5182,14 +5235,14 @@
       <c r="F177" s="23"/>
     </row>
     <row r="178" spans="1:34" ht="141" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="65" t="s">
-        <v>171</v>
-      </c>
-      <c r="B178" s="69"/>
-      <c r="C178" s="69"/>
-      <c r="D178" s="69"/>
-      <c r="E178" s="69"/>
-      <c r="F178" s="69"/>
+      <c r="A178" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="B178" s="72"/>
+      <c r="C178" s="72"/>
+      <c r="D178" s="72"/>
+      <c r="E178" s="72"/>
+      <c r="F178" s="72"/>
     </row>
     <row r="179" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="36"/>
@@ -5200,27 +5253,27 @@
       <c r="F179" s="23"/>
     </row>
     <row r="180" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B180" s="73"/>
-      <c r="C180" s="73"/>
-      <c r="D180" s="73"/>
-      <c r="E180" s="73"/>
-      <c r="F180" s="73"/>
+      <c r="A180" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B180" s="76"/>
+      <c r="C180" s="76"/>
+      <c r="D180" s="76"/>
+      <c r="E180" s="76"/>
+      <c r="F180" s="76"/>
     </row>
     <row r="181" spans="1:34" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="70" t="s">
-        <v>140</v>
-      </c>
-      <c r="B181" s="71"/>
-      <c r="C181" s="72"/>
-      <c r="D181" s="72"/>
-      <c r="E181" s="72"/>
-      <c r="F181" s="72"/>
+      <c r="A181" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="B181" s="74"/>
+      <c r="C181" s="75"/>
+      <c r="D181" s="75"/>
+      <c r="E181" s="75"/>
+      <c r="F181" s="75"/>
     </row>
     <row r="182" spans="1:34" s="57" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="90"/>
+      <c r="A182" s="65"/>
       <c r="B182" s="61" t="s">
         <v>5</v>
       </c>
@@ -5267,7 +5320,7 @@
     </row>
     <row r="183" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B183" s="60" t="s">
         <v>3</v>
@@ -5286,7 +5339,7 @@
     <row r="184" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="34"/>
       <c r="B184" s="46" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C184" s="14"/>
       <c r="D184" s="14"/>
@@ -5302,7 +5355,7 @@
     <row r="185" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="34"/>
       <c r="B185" s="46" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="C185" s="14"/>
       <c r="D185" s="14"/>
@@ -5318,7 +5371,7 @@
     <row r="186" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="34"/>
       <c r="B186" s="46" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="C186" s="14"/>
       <c r="D186" s="14"/>
@@ -5334,7 +5387,7 @@
     <row r="187" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="34"/>
       <c r="B187" s="46" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C187" s="14"/>
       <c r="D187" s="14"/>
@@ -5350,7 +5403,7 @@
     <row r="188" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="34"/>
       <c r="B188" s="46" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="C188" s="14"/>
       <c r="D188" s="14"/>
@@ -5366,7 +5419,7 @@
     <row r="189" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="34"/>
       <c r="B189" s="46" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C189" s="14"/>
       <c r="D189" s="14"/>
@@ -5382,7 +5435,7 @@
     <row r="190" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="34"/>
       <c r="B190" s="46" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C190" s="14"/>
       <c r="D190" s="14"/>
@@ -5398,7 +5451,7 @@
     <row r="191" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="34"/>
       <c r="B191" s="46" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C191" s="14"/>
       <c r="D191" s="14"/>
@@ -5414,7 +5467,7 @@
     <row r="192" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="34"/>
       <c r="B192" s="46" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C192" s="14"/>
       <c r="D192" s="14"/>
@@ -5430,7 +5483,7 @@
     <row r="193" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="34"/>
       <c r="B193" s="46" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="C193" s="14"/>
       <c r="D193" s="14"/>
@@ -5446,7 +5499,7 @@
     <row r="194" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="34"/>
       <c r="B194" s="46" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C194" s="14"/>
       <c r="D194" s="14"/>
@@ -5462,7 +5515,7 @@
     <row r="195" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="34"/>
       <c r="B195" s="46" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C195" s="14"/>
       <c r="D195" s="14"/>
@@ -5478,7 +5531,7 @@
     <row r="196" spans="1:34" s="24" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="34"/>
       <c r="B196" s="46" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="C196" s="14"/>
       <c r="D196" s="14"/>
@@ -5494,7 +5547,7 @@
     <row r="197" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="34"/>
       <c r="B197" s="46" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="C197" s="14"/>
       <c r="D197" s="14"/>
@@ -5510,7 +5563,7 @@
     <row r="198" spans="1:34" s="3" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="64"/>
       <c r="B198" s="46" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C198" s="33"/>
       <c r="D198" s="33"/>
@@ -5554,7 +5607,7 @@
     <row r="199" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="34"/>
       <c r="B199" s="46" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="C199" s="14"/>
       <c r="D199" s="14"/>
@@ -5570,7 +5623,7 @@
     <row r="200" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="34"/>
       <c r="B200" s="46" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C200" s="14"/>
       <c r="D200" s="14"/>
@@ -5586,7 +5639,7 @@
     <row r="201" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="34"/>
       <c r="B201" s="46" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C201" s="14"/>
       <c r="D201" s="14"/>
@@ -5602,7 +5655,7 @@
     <row r="202" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="34"/>
       <c r="B202" s="46" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="C202" s="14"/>
       <c r="D202" s="14"/>
@@ -5618,7 +5671,7 @@
     <row r="203" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="34"/>
       <c r="B203" s="46" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="C203" s="14"/>
       <c r="D203" s="14"/>
@@ -5634,7 +5687,7 @@
     <row r="204" spans="1:34" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="34"/>
       <c r="B204" s="46" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="C204" s="14"/>
       <c r="D204" s="14"/>
@@ -5649,7 +5702,7 @@
     </row>
     <row r="205" spans="1:34" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="36" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B205" s="54"/>
       <c r="C205" s="24"/>
@@ -5658,14 +5711,14 @@
       <c r="F205" s="24"/>
     </row>
     <row r="206" spans="1:34" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="65" t="s">
-        <v>171</v>
-      </c>
-      <c r="B206" s="69"/>
-      <c r="C206" s="69"/>
-      <c r="D206" s="69"/>
-      <c r="E206" s="69"/>
-      <c r="F206" s="69"/>
+      <c r="A206" s="68" t="s">
+        <v>150</v>
+      </c>
+      <c r="B206" s="72"/>
+      <c r="C206" s="72"/>
+      <c r="D206" s="72"/>
+      <c r="E206" s="72"/>
+      <c r="F206" s="72"/>
     </row>
     <row r="207" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="36"/>
@@ -5676,27 +5729,27 @@
       <c r="F207" s="24"/>
     </row>
     <row r="208" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B208" s="73"/>
-      <c r="C208" s="73"/>
-      <c r="D208" s="73"/>
-      <c r="E208" s="73"/>
-      <c r="F208" s="73"/>
+      <c r="A208" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B208" s="76"/>
+      <c r="C208" s="76"/>
+      <c r="D208" s="76"/>
+      <c r="E208" s="76"/>
+      <c r="F208" s="76"/>
     </row>
     <row r="209" spans="1:34" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="70" t="s">
-        <v>141</v>
-      </c>
-      <c r="B209" s="71"/>
-      <c r="C209" s="72"/>
-      <c r="D209" s="72"/>
-      <c r="E209" s="72"/>
-      <c r="F209" s="72"/>
+      <c r="A209" s="73" t="s">
+        <v>119</v>
+      </c>
+      <c r="B209" s="74"/>
+      <c r="C209" s="75"/>
+      <c r="D209" s="75"/>
+      <c r="E209" s="75"/>
+      <c r="F209" s="75"/>
     </row>
     <row r="210" spans="1:34" s="57" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="90"/>
+      <c r="A210" s="65"/>
       <c r="B210" s="61" t="s">
         <v>5</v>
       </c>
@@ -5743,7 +5796,7 @@
     </row>
     <row r="211" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B211" s="60" t="s">
         <v>3</v>
@@ -5762,7 +5815,7 @@
     <row r="212" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="34"/>
       <c r="B212" s="46" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C212" s="14"/>
       <c r="D212" s="14"/>
@@ -5778,7 +5831,7 @@
     <row r="213" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="34"/>
       <c r="B213" s="46" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="C213" s="14"/>
       <c r="D213" s="14"/>
@@ -5794,7 +5847,7 @@
     <row r="214" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="34"/>
       <c r="B214" s="46" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C214" s="14"/>
       <c r="D214" s="14"/>
@@ -5809,7 +5862,7 @@
     </row>
     <row r="215" spans="1:34" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="58" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B215" s="56"/>
       <c r="C215" s="1"/>
@@ -5818,14 +5871,14 @@
       <c r="F215" s="1"/>
     </row>
     <row r="216" spans="1:34" ht="142.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="65" t="s">
-        <v>172</v>
-      </c>
-      <c r="B216" s="69"/>
-      <c r="C216" s="69"/>
-      <c r="D216" s="69"/>
-      <c r="E216" s="69"/>
-      <c r="F216" s="69"/>
+      <c r="A216" s="68" t="s">
+        <v>151</v>
+      </c>
+      <c r="B216" s="72"/>
+      <c r="C216" s="72"/>
+      <c r="D216" s="72"/>
+      <c r="E216" s="72"/>
+      <c r="F216" s="72"/>
     </row>
     <row r="217" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="58"/>
@@ -5836,27 +5889,27 @@
       <c r="F217" s="1"/>
     </row>
     <row r="218" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B218" s="73"/>
-      <c r="C218" s="73"/>
-      <c r="D218" s="73"/>
-      <c r="E218" s="73"/>
-      <c r="F218" s="73"/>
+      <c r="A218" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B218" s="76"/>
+      <c r="C218" s="76"/>
+      <c r="D218" s="76"/>
+      <c r="E218" s="76"/>
+      <c r="F218" s="76"/>
     </row>
     <row r="219" spans="1:34" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="70" t="s">
-        <v>142</v>
-      </c>
-      <c r="B219" s="71"/>
-      <c r="C219" s="72"/>
-      <c r="D219" s="72"/>
-      <c r="E219" s="72"/>
-      <c r="F219" s="72"/>
+      <c r="A219" s="73" t="s">
+        <v>120</v>
+      </c>
+      <c r="B219" s="74"/>
+      <c r="C219" s="75"/>
+      <c r="D219" s="75"/>
+      <c r="E219" s="75"/>
+      <c r="F219" s="75"/>
     </row>
     <row r="220" spans="1:34" s="57" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="90"/>
+      <c r="A220" s="65"/>
       <c r="B220" s="61" t="s">
         <v>5</v>
       </c>
@@ -5903,7 +5956,7 @@
     </row>
     <row r="221" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="59" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B221" s="60" t="s">
         <v>3</v>
@@ -5922,7 +5975,7 @@
     <row r="222" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="34"/>
       <c r="B222" s="46" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="C222" s="14"/>
       <c r="D222" s="14"/>
@@ -5938,7 +5991,7 @@
     <row r="223" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="34"/>
       <c r="B223" s="46" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C223" s="14"/>
       <c r="D223" s="14"/>
@@ -5954,7 +6007,7 @@
     <row r="224" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="34"/>
       <c r="B224" s="46" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C224" s="14"/>
       <c r="D224" s="14"/>
@@ -5970,7 +6023,7 @@
     <row r="225" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="34"/>
       <c r="B225" s="46" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C225" s="14"/>
       <c r="D225" s="14"/>
@@ -5986,7 +6039,7 @@
     <row r="226" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="34"/>
       <c r="B226" s="46" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="C226" s="14"/>
       <c r="D226" s="14"/>
@@ -6002,7 +6055,7 @@
     <row r="227" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="34"/>
       <c r="B227" s="46" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="C227" s="14"/>
       <c r="D227" s="14"/>
@@ -6018,7 +6071,7 @@
     <row r="228" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="34"/>
       <c r="B228" s="46" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="C228" s="14"/>
       <c r="D228" s="14"/>
@@ -6034,7 +6087,7 @@
     <row r="229" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="34"/>
       <c r="B229" s="46" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="C229" s="14"/>
       <c r="D229" s="14"/>
@@ -6050,7 +6103,7 @@
     <row r="230" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="34"/>
       <c r="B230" s="46" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="C230" s="14"/>
       <c r="D230" s="14"/>
@@ -6066,7 +6119,7 @@
     <row r="231" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="34"/>
       <c r="B231" s="47" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="C231" s="14"/>
       <c r="D231" s="14"/>
@@ -6082,7 +6135,7 @@
     <row r="232" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="34"/>
       <c r="B232" s="49" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C232" s="14"/>
       <c r="D232" s="14"/>
@@ -6098,7 +6151,7 @@
     <row r="233" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="34"/>
       <c r="B233" s="49" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C233" s="14"/>
       <c r="D233" s="14"/>
@@ -6114,7 +6167,7 @@
     <row r="234" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="34"/>
       <c r="B234" s="46" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C234" s="14"/>
       <c r="D234" s="14"/>
@@ -6130,7 +6183,7 @@
     <row r="235" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="34"/>
       <c r="B235" s="46" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C235" s="14"/>
       <c r="D235" s="14"/>
@@ -6146,7 +6199,7 @@
     <row r="236" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="34"/>
       <c r="B236" s="46" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C236" s="14"/>
       <c r="D236" s="14"/>
@@ -6162,7 +6215,7 @@
     <row r="237" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="34"/>
       <c r="B237" s="46" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C237" s="14"/>
       <c r="D237" s="14"/>
@@ -6178,7 +6231,7 @@
     <row r="238" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="34"/>
       <c r="B238" s="46" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C238" s="14"/>
       <c r="D238" s="14"/>
@@ -6194,7 +6247,7 @@
     <row r="239" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="34"/>
       <c r="B239" s="46" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C239" s="14"/>
       <c r="D239" s="14"/>
@@ -6210,7 +6263,7 @@
     <row r="240" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="34"/>
       <c r="B240" s="46" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="C240" s="14"/>
       <c r="D240" s="14"/>
@@ -6226,7 +6279,7 @@
     <row r="241" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="34"/>
       <c r="B241" s="46" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="C241" s="14"/>
       <c r="D241" s="14"/>
@@ -6242,7 +6295,7 @@
     <row r="242" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="34"/>
       <c r="B242" s="46" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C242" s="14"/>
       <c r="D242" s="14"/>
@@ -6258,7 +6311,7 @@
     <row r="243" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="34"/>
       <c r="B243" s="46" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="C243" s="14"/>
       <c r="D243" s="14"/>
@@ -6274,7 +6327,7 @@
     <row r="244" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="34"/>
       <c r="B244" s="46" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C244" s="14"/>
       <c r="D244" s="14"/>
@@ -6290,7 +6343,7 @@
     <row r="245" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="34"/>
       <c r="B245" s="46" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C245" s="14"/>
       <c r="D245" s="14"/>
@@ -6306,7 +6359,7 @@
     <row r="246" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="34"/>
       <c r="B246" s="46" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C246" s="14"/>
       <c r="D246" s="14"/>
@@ -6322,7 +6375,7 @@
     <row r="247" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="34"/>
       <c r="B247" s="46" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C247" s="14"/>
       <c r="D247" s="14"/>
@@ -6338,7 +6391,7 @@
     <row r="248" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="34"/>
       <c r="B248" s="46" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="C248" s="14"/>
       <c r="D248" s="14"/>
@@ -6354,7 +6407,7 @@
     <row r="249" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="34"/>
       <c r="B249" s="46" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C249" s="14"/>
       <c r="D249" s="14"/>
@@ -6370,7 +6423,7 @@
     <row r="250" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="34"/>
       <c r="B250" s="46" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C250" s="14"/>
       <c r="D250" s="14"/>
@@ -6386,7 +6439,7 @@
     <row r="251" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="34"/>
       <c r="B251" s="46" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C251" s="14"/>
       <c r="D251" s="14"/>
@@ -6402,7 +6455,7 @@
     <row r="252" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="34"/>
       <c r="B252" s="46" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="C252" s="14"/>
       <c r="D252" s="14"/>
@@ -6418,7 +6471,7 @@
     <row r="253" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="34"/>
       <c r="B253" s="46" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="C253" s="14"/>
       <c r="D253" s="14"/>
@@ -6434,7 +6487,7 @@
     <row r="254" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="34"/>
       <c r="B254" s="46" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="C254" s="14"/>
       <c r="D254" s="14"/>
@@ -6450,7 +6503,7 @@
     <row r="255" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="34"/>
       <c r="B255" s="46" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="C255" s="14"/>
       <c r="D255" s="14"/>
@@ -6466,7 +6519,7 @@
     <row r="256" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="34"/>
       <c r="B256" s="46" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="C256" s="14"/>
       <c r="D256" s="14"/>
@@ -6482,7 +6535,7 @@
     <row r="257" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="34"/>
       <c r="B257" s="46" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="C257" s="14"/>
       <c r="D257" s="14"/>
@@ -6497,18 +6550,18 @@
     </row>
     <row r="258" spans="1:6" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="40" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
     </row>
     <row r="259" spans="1:6" ht="138" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="65" t="s">
-        <v>173</v>
-      </c>
-      <c r="B259" s="65"/>
-      <c r="C259" s="65"/>
-      <c r="D259" s="65"/>
-      <c r="E259" s="65"/>
-      <c r="F259" s="65"/>
+      <c r="A259" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="B259" s="68"/>
+      <c r="C259" s="68"/>
+      <c r="D259" s="68"/>
+      <c r="E259" s="68"/>
+      <c r="F259" s="68"/>
     </row>
   </sheetData>
   <sortState ref="A132:B174">
@@ -6577,24 +6630,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
+      <c r="A1" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
     </row>
     <row r="2" spans="1:6" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="89"/>
+      <c r="A2" s="90" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="92"/>
     </row>
     <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -6616,7 +6669,7 @@
     </row>
     <row r="4" spans="1:6" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>3</v>
@@ -6637,7 +6690,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -6656,7 +6709,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -6675,7 +6728,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -6694,7 +6747,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
